--- a/StructureDefinition-mii-pr-mikrobio-allgemeine-bestimmung.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-allgemeine-bestimmung.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5876" uniqueCount="779">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5875" uniqueCount="780">
   <si>
     <t>Property</t>
   </si>
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>MII PR Mikrobio Allgemeine Bestimmung</t>
+    <t>MII PR Mikrobio Allgemeine Bestimmung (Identifizierung)</t>
   </si>
   <si>
     <t>Status</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T16:03:21+00:00</t>
+    <t>2026-09-10T13:00:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1346,6 +1346,9 @@
 </t>
   </si>
   <si>
+    <t>Bevorzugt 41852-5 'Microorganism or agent identified in Specimen'. Benennt das Labor die Erregergruppe (Bakterien, Pilze, Viren) oder das Sequenzierziel (16S, 18S rRNA) im Code, sind die entsprechenden Codes gleichwertig zulaessig. Es werden bevorzugt LOINC-Codes ohne praekoordinierte Specimentype-Angabe verwendet (System = XXX); der Specimentype wird separat ueber Specimen.type kodiert.</t>
+  </si>
+  <si>
     <t>LOINC-Code, der den gemessenen Laborparameter bzw. durchgeführten Labortest beschreibt.</t>
   </si>
   <si>
@@ -1355,18 +1358,7 @@
     <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
   </si>
   <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="http://loinc.org"/&gt;
-    &lt;code value="41852-5"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
-    <t>Codes identifying names of simple observations.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/ValueSet/mii-vs-mikrobio-allgemeine-bestimmung-tests-loinc</t>
   </si>
   <si>
     <t>Observation.code.id</t>
@@ -2129,7 +2121,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-probe)
 </t>
   </si>
   <si>
@@ -2409,6 +2401,12 @@
   </si>
   <si>
     <t>*All* code-value and  component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
+  </si>
+  <si>
+    <t>Codes identifying names of simple observations.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
   </si>
   <si>
     <t>Observation.component.value[x]</t>
@@ -9706,16 +9704,16 @@
         <v>282</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>63</v>
+        <v>422</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>76</v>
@@ -9725,7 +9723,7 @@
         <v>76</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>425</v>
+        <v>76</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>76</v>
@@ -9740,13 +9738,11 @@
         <v>76</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="Y68" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="Y68" s="2"/>
+      <c r="Z68" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>427</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>76</v>
@@ -9781,10 +9777,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9881,10 +9877,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9983,10 +9979,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10085,10 +10081,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10185,10 +10181,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10287,10 +10283,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10391,10 +10387,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10493,10 +10489,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10597,10 +10593,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10701,10 +10697,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10805,13 +10801,13 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="C79" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="C79" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="D79" t="s" s="2">
         <v>76</v>
@@ -10855,7 +10851,7 @@
         <v>76</v>
       </c>
       <c r="S79" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="T79" t="s" s="2">
         <v>76</v>
@@ -10873,10 +10869,10 @@
         <v>141</v>
       </c>
       <c r="Y79" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="Z79" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="Z79" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>76</v>
@@ -10911,10 +10907,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11015,10 +11011,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11041,19 +11037,19 @@
         <v>84</v>
       </c>
       <c r="K81" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="L81" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="L81" t="s" s="2">
+      <c r="M81" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="M81" t="s" s="2">
+      <c r="N81" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="N81" t="s" s="2">
+      <c r="O81" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>76</v>
@@ -11102,7 +11098,7 @@
         <v>76</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>74</v>
@@ -11119,10 +11115,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11219,10 +11215,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11321,10 +11317,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11350,13 +11346,13 @@
         <v>98</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -11406,16 +11402,16 @@
         <v>76</v>
       </c>
       <c r="AF84" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI84" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="AG84" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH84" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI84" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>91</v>
@@ -11423,10 +11419,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11452,13 +11448,13 @@
         <v>125</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="M85" t="s" s="2">
+      <c r="N85" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -11487,28 +11483,28 @@
         <v>141</v>
       </c>
       <c r="Y85" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="Z85" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="Z85" t="s" s="2">
+      <c r="AA85" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF85" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>74</v>
@@ -11525,10 +11521,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11554,13 +11550,13 @@
         <v>258</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="N86" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>468</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -11610,7 +11606,7 @@
         <v>76</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>74</v>
@@ -11627,10 +11623,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11656,13 +11652,13 @@
         <v>98</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -11712,7 +11708,7 @@
         <v>76</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>74</v>
@@ -11729,10 +11725,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11755,16 +11751,16 @@
         <v>84</v>
       </c>
       <c r="K88" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="L88" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="L88" t="s" s="2">
+      <c r="M88" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="N88" t="s" s="2">
         <v>478</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>479</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -11814,7 +11810,7 @@
         <v>76</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>74</v>
@@ -11831,14 +11827,14 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -11857,19 +11853,19 @@
         <v>84</v>
       </c>
       <c r="K89" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="L89" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="L89" t="s" s="2">
+      <c r="M89" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="M89" t="s" s="2">
+      <c r="N89" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="N89" t="s" s="2">
+      <c r="O89" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>486</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>76</v>
@@ -11918,7 +11914,7 @@
         <v>76</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>74</v>
@@ -11935,10 +11931,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12035,10 +12031,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12137,10 +12133,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12166,13 +12162,13 @@
         <v>98</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -12222,16 +12218,16 @@
         <v>76</v>
       </c>
       <c r="AF92" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI92" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="AG92" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH92" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI92" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>91</v>
@@ -12239,10 +12235,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12268,13 +12264,13 @@
         <v>125</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="N93" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -12303,28 +12299,28 @@
         <v>141</v>
       </c>
       <c r="Y93" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="Z93" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="Z93" t="s" s="2">
+      <c r="AA93" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF93" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="AA93" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB93" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD93" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE93" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF93" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>74</v>
@@ -12341,10 +12337,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12370,13 +12366,13 @@
         <v>258</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>468</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -12426,7 +12422,7 @@
         <v>76</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>74</v>
@@ -12443,10 +12439,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12472,13 +12468,13 @@
         <v>98</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="M95" t="s" s="2">
+      <c r="N95" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -12528,7 +12524,7 @@
         <v>76</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>74</v>
@@ -12545,14 +12541,14 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -12571,19 +12567,19 @@
         <v>84</v>
       </c>
       <c r="K96" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="L96" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="L96" t="s" s="2">
+      <c r="M96" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="M96" t="s" s="2">
+      <c r="N96" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="N96" t="s" s="2">
+      <c r="O96" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>76</v>
@@ -12632,7 +12628,7 @@
         <v>76</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>74</v>
@@ -12644,15 +12640,15 @@
         <v>90</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12749,10 +12745,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12851,13 +12847,13 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="C99" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="C99" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="D99" t="s" s="2">
         <v>103</v>
@@ -12879,13 +12875,13 @@
         <v>76</v>
       </c>
       <c r="K99" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="L99" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="L99" t="s" s="2">
+      <c r="M99" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>107</v>
@@ -12955,10 +12951,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12981,13 +12977,13 @@
         <v>76</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -13038,7 +13034,7 @@
         <v>76</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>74</v>
@@ -13055,10 +13051,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13084,13 +13080,13 @@
         <v>119</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="M101" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -13140,7 +13136,7 @@
         <v>76</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>74</v>
@@ -13157,10 +13153,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13183,19 +13179,19 @@
         <v>84</v>
       </c>
       <c r="K102" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="L102" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="L102" t="s" s="2">
+      <c r="M102" t="s" s="2">
         <v>517</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="N102" t="s" s="2">
         <v>388</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>76</v>
@@ -13244,7 +13240,7 @@
         <v>76</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>74</v>
@@ -13261,10 +13257,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13290,16 +13286,16 @@
         <v>282</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="M103" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="M103" t="s" s="2">
+      <c r="N103" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="N103" t="s" s="2">
+      <c r="O103" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>76</v>
@@ -13336,26 +13332,26 @@
         <v>76</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AC103" s="2"/>
       <c r="AD103" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE103" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI103" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="AF103" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="AG103" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI103" t="s" s="2">
-        <v>527</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>91</v>
@@ -13363,13 +13359,13 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="C104" t="s" s="2">
         <v>528</v>
-      </c>
-      <c r="B104" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="C104" t="s" s="2">
-        <v>529</v>
       </c>
       <c r="D104" t="s" s="2">
         <v>76</v>
@@ -13394,16 +13390,16 @@
         <v>282</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="M104" t="s" s="2">
-        <v>531</v>
-      </c>
       <c r="N104" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="O104" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>76</v>
@@ -13432,7 +13428,7 @@
       </c>
       <c r="Y104" s="2"/>
       <c r="Z104" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>76</v>
@@ -13450,7 +13446,7 @@
         <v>76</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>74</v>
@@ -13459,7 +13455,7 @@
         <v>83</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>91</v>
@@ -13467,10 +13463,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="B105" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="B105" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13567,10 +13563,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="B106" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="B106" t="s" s="2">
-        <v>536</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13669,10 +13665,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="B107" t="s" s="2">
         <v>537</v>
-      </c>
-      <c r="B107" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -13773,10 +13769,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="B108" t="s" s="2">
         <v>539</v>
-      </c>
-      <c r="B108" t="s" s="2">
-        <v>540</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13873,10 +13869,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="B109" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="B109" t="s" s="2">
-        <v>542</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13975,10 +13971,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="B110" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="B110" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14079,10 +14075,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="B111" t="s" s="2">
         <v>545</v>
-      </c>
-      <c r="B111" t="s" s="2">
-        <v>546</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14181,10 +14177,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="B112" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="B112" t="s" s="2">
-        <v>548</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14285,10 +14281,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="B113" t="s" s="2">
         <v>549</v>
-      </c>
-      <c r="B113" t="s" s="2">
-        <v>550</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14389,10 +14385,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="B114" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="B114" t="s" s="2">
-        <v>552</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -14493,10 +14489,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="B115" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="B115" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -14597,13 +14593,13 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="C116" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="B116" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="C116" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="D116" t="s" s="2">
         <v>76</v>
@@ -14625,19 +14621,19 @@
         <v>84</v>
       </c>
       <c r="K116" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="L116" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="L116" t="s" s="2">
-        <v>558</v>
-      </c>
       <c r="M116" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="N116" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="O116" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="O116" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>76</v>
@@ -14686,7 +14682,7 @@
         <v>76</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>74</v>
@@ -14695,7 +14691,7 @@
         <v>83</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="AJ116" t="s" s="2">
         <v>91</v>
@@ -14703,10 +14699,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -14803,10 +14799,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -14905,13 +14901,13 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="C119" t="s" s="2">
         <v>561</v>
-      </c>
-      <c r="B119" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="C119" t="s" s="2">
-        <v>562</v>
       </c>
       <c r="D119" t="s" s="2">
         <v>103</v>
@@ -14933,16 +14929,16 @@
         <v>76</v>
       </c>
       <c r="K119" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="L119" t="s" s="2">
         <v>563</v>
       </c>
-      <c r="L119" t="s" s="2">
+      <c r="M119" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="M119" t="s" s="2">
+      <c r="N119" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>566</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -15009,10 +15005,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="B120" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="B120" t="s" s="2">
-        <v>568</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15035,19 +15031,19 @@
         <v>84</v>
       </c>
       <c r="K120" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="L120" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="L120" t="s" s="2">
+      <c r="M120" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="M120" t="s" s="2">
+      <c r="N120" t="s" s="2">
         <v>571</v>
       </c>
-      <c r="N120" t="s" s="2">
+      <c r="O120" t="s" s="2">
         <v>572</v>
-      </c>
-      <c r="O120" t="s" s="2">
-        <v>573</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>76</v>
@@ -15096,7 +15092,7 @@
         <v>76</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>74</v>
@@ -15113,10 +15109,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="B121" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="B121" t="s" s="2">
-        <v>576</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -15213,10 +15209,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="B122" t="s" s="2">
         <v>577</v>
-      </c>
-      <c r="B122" t="s" s="2">
-        <v>578</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -15315,13 +15311,13 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="C123" t="s" s="2">
         <v>579</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="C123" t="s" s="2">
-        <v>580</v>
       </c>
       <c r="D123" t="s" s="2">
         <v>103</v>
@@ -15343,16 +15339,16 @@
         <v>76</v>
       </c>
       <c r="K123" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="L123" t="s" s="2">
         <v>581</v>
       </c>
-      <c r="L123" t="s" s="2">
+      <c r="M123" t="s" s="2">
         <v>582</v>
       </c>
-      <c r="M123" t="s" s="2">
+      <c r="N123" t="s" s="2">
         <v>583</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>584</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -15419,10 +15415,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="B124" t="s" s="2">
         <v>585</v>
-      </c>
-      <c r="B124" t="s" s="2">
-        <v>586</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -15445,13 +15441,13 @@
         <v>76</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -15502,7 +15498,7 @@
         <v>76</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>74</v>
@@ -15519,10 +15515,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="B125" t="s" s="2">
         <v>589</v>
-      </c>
-      <c r="B125" t="s" s="2">
-        <v>590</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -15548,22 +15544,22 @@
         <v>159</v>
       </c>
       <c r="L125" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="M125" t="s" s="2">
         <v>591</v>
-      </c>
-      <c r="M125" t="s" s="2">
-        <v>592</v>
       </c>
       <c r="N125" t="s" s="2">
         <v>327</v>
       </c>
       <c r="O125" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="P125" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q125" t="s" s="2">
         <v>593</v>
-      </c>
-      <c r="P125" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q125" t="s" s="2">
-        <v>594</v>
       </c>
       <c r="R125" t="s" s="2">
         <v>76</v>
@@ -15587,28 +15583,28 @@
         <v>225</v>
       </c>
       <c r="Y125" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="Z125" t="s" s="2">
         <v>595</v>
       </c>
-      <c r="Z125" t="s" s="2">
+      <c r="AA125" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB125" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC125" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD125" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE125" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF125" t="s" s="2">
         <v>596</v>
-      </c>
-      <c r="AA125" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB125" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC125" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD125" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE125" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF125" t="s" s="2">
-        <v>597</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>74</v>
@@ -15625,10 +15621,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="B126" t="s" s="2">
         <v>598</v>
-      </c>
-      <c r="B126" t="s" s="2">
-        <v>599</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -15654,16 +15650,16 @@
         <v>98</v>
       </c>
       <c r="L126" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="M126" t="s" s="2">
         <v>600</v>
-      </c>
-      <c r="M126" t="s" s="2">
-        <v>601</v>
       </c>
       <c r="N126" t="s" s="2">
         <v>327</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>76</v>
@@ -15712,7 +15708,7 @@
         <v>76</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>74</v>
@@ -15729,10 +15725,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="B127" t="s" s="2">
         <v>604</v>
-      </c>
-      <c r="B127" t="s" s="2">
-        <v>605</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -15758,74 +15754,74 @@
         <v>125</v>
       </c>
       <c r="L127" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="M127" t="s" s="2">
         <v>606</v>
       </c>
-      <c r="M127" t="s" s="2">
+      <c r="N127" t="s" s="2">
         <v>607</v>
       </c>
-      <c r="N127" t="s" s="2">
+      <c r="O127" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="O127" t="s" s="2">
-        <v>609</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q127" s="2"/>
       <c r="R127" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="S127" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T127" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U127" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V127" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W127" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X127" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y127" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z127" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA127" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB127" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC127" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD127" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE127" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF127" t="s" s="2">
         <v>610</v>
       </c>
-      <c r="S127" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T127" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U127" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V127" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W127" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X127" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y127" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z127" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA127" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB127" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC127" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD127" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE127" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF127" t="s" s="2">
+      <c r="AG127" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH127" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI127" t="s" s="2">
         <v>611</v>
-      </c>
-      <c r="AG127" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH127" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI127" t="s" s="2">
-        <v>612</v>
       </c>
       <c r="AJ127" t="s" s="2">
         <v>91</v>
@@ -15833,10 +15829,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="B128" t="s" s="2">
         <v>613</v>
-      </c>
-      <c r="B128" t="s" s="2">
-        <v>614</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -15862,16 +15858,16 @@
         <v>159</v>
       </c>
       <c r="L128" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="M128" t="s" s="2">
         <v>615</v>
       </c>
-      <c r="M128" t="s" s="2">
+      <c r="N128" t="s" s="2">
         <v>616</v>
       </c>
-      <c r="N128" t="s" s="2">
+      <c r="O128" t="s" s="2">
         <v>617</v>
-      </c>
-      <c r="O128" t="s" s="2">
-        <v>618</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>76</v>
@@ -15920,7 +15916,7 @@
         <v>76</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>74</v>
@@ -15937,13 +15933,13 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="C129" t="s" s="2">
         <v>620</v>
-      </c>
-      <c r="B129" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="C129" t="s" s="2">
-        <v>621</v>
       </c>
       <c r="D129" t="s" s="2">
         <v>76</v>
@@ -15965,19 +15961,19 @@
         <v>84</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="N129" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="O129" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="O129" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>76</v>
@@ -16026,7 +16022,7 @@
         <v>76</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>74</v>
@@ -16035,7 +16031,7 @@
         <v>83</v>
       </c>
       <c r="AI129" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="AJ129" t="s" s="2">
         <v>91</v>
@@ -16043,13 +16039,13 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="C130" t="s" s="2">
         <v>623</v>
-      </c>
-      <c r="B130" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="C130" t="s" s="2">
-        <v>624</v>
       </c>
       <c r="D130" t="s" s="2">
         <v>76</v>
@@ -16071,19 +16067,19 @@
         <v>84</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="N130" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="O130" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="O130" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>76</v>
@@ -16132,7 +16128,7 @@
         <v>76</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>74</v>
@@ -16141,7 +16137,7 @@
         <v>83</v>
       </c>
       <c r="AI130" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="AJ130" t="s" s="2">
         <v>91</v>
@@ -16149,10 +16145,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -16178,16 +16174,16 @@
         <v>282</v>
       </c>
       <c r="L131" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="M131" t="s" s="2">
         <v>627</v>
       </c>
-      <c r="M131" t="s" s="2">
+      <c r="N131" t="s" s="2">
         <v>628</v>
       </c>
-      <c r="N131" t="s" s="2">
+      <c r="O131" t="s" s="2">
         <v>629</v>
-      </c>
-      <c r="O131" t="s" s="2">
-        <v>630</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>76</v>
@@ -16216,34 +16212,34 @@
       </c>
       <c r="Y131" s="2"/>
       <c r="Z131" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="AA131" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB131" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC131" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD131" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE131" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF131" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="AG131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH131" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI131" t="s" s="2">
         <v>631</v>
-      </c>
-      <c r="AA131" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB131" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC131" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD131" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE131" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF131" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="AG131" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH131" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI131" t="s" s="2">
-        <v>632</v>
       </c>
       <c r="AJ131" t="s" s="2">
         <v>91</v>
@@ -16251,14 +16247,14 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
@@ -16280,16 +16276,16 @@
         <v>282</v>
       </c>
       <c r="L132" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="M132" t="s" s="2">
         <v>635</v>
       </c>
-      <c r="M132" t="s" s="2">
+      <c r="N132" t="s" s="2">
         <v>636</v>
       </c>
-      <c r="N132" t="s" s="2">
+      <c r="O132" t="s" s="2">
         <v>637</v>
-      </c>
-      <c r="O132" t="s" s="2">
-        <v>638</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>76</v>
@@ -16317,11 +16313,11 @@
         <v>141</v>
       </c>
       <c r="Y132" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="Z132" t="s" s="2">
         <v>639</v>
       </c>
-      <c r="Z132" t="s" s="2">
-        <v>640</v>
-      </c>
       <c r="AA132" t="s" s="2">
         <v>76</v>
       </c>
@@ -16338,7 +16334,7 @@
         <v>76</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>74</v>
@@ -16355,10 +16351,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -16381,19 +16377,19 @@
         <v>76</v>
       </c>
       <c r="K133" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="L133" t="s" s="2">
         <v>642</v>
       </c>
-      <c r="L133" t="s" s="2">
+      <c r="M133" t="s" s="2">
         <v>643</v>
       </c>
-      <c r="M133" t="s" s="2">
+      <c r="N133" t="s" s="2">
         <v>644</v>
       </c>
-      <c r="N133" t="s" s="2">
+      <c r="O133" t="s" s="2">
         <v>645</v>
-      </c>
-      <c r="O133" t="s" s="2">
-        <v>646</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>76</v>
@@ -16442,7 +16438,7 @@
         <v>76</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>74</v>
@@ -16459,10 +16455,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -16488,13 +16484,13 @@
         <v>282</v>
       </c>
       <c r="L134" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="M134" t="s" s="2">
         <v>648</v>
       </c>
-      <c r="M134" t="s" s="2">
+      <c r="N134" t="s" s="2">
         <v>649</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>650</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -16523,11 +16519,11 @@
         <v>149</v>
       </c>
       <c r="Y134" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="Z134" t="s" s="2">
         <v>651</v>
       </c>
-      <c r="Z134" t="s" s="2">
-        <v>652</v>
-      </c>
       <c r="AA134" t="s" s="2">
         <v>76</v>
       </c>
@@ -16544,7 +16540,7 @@
         <v>76</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>74</v>
@@ -16561,10 +16557,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -16590,16 +16586,16 @@
         <v>282</v>
       </c>
       <c r="L135" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="M135" t="s" s="2">
         <v>654</v>
       </c>
-      <c r="M135" t="s" s="2">
+      <c r="N135" t="s" s="2">
         <v>655</v>
       </c>
-      <c r="N135" t="s" s="2">
+      <c r="O135" t="s" s="2">
         <v>656</v>
-      </c>
-      <c r="O135" t="s" s="2">
-        <v>657</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>76</v>
@@ -16628,7 +16624,7 @@
       </c>
       <c r="Y135" s="2"/>
       <c r="Z135" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>76</v>
@@ -16646,7 +16642,7 @@
         <v>76</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>74</v>
@@ -16663,10 +16659,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -16763,10 +16759,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -16865,10 +16861,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -16969,10 +16965,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -17069,10 +17065,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -17171,10 +17167,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -17275,10 +17271,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -17377,10 +17373,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -17481,10 +17477,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -17585,10 +17581,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -17689,10 +17685,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -17793,10 +17789,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -17819,16 +17815,16 @@
         <v>76</v>
       </c>
       <c r="K147" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="L147" t="s" s="2">
         <v>671</v>
       </c>
-      <c r="L147" t="s" s="2">
+      <c r="M147" t="s" s="2">
         <v>672</v>
       </c>
-      <c r="M147" t="s" s="2">
+      <c r="N147" t="s" s="2">
         <v>673</v>
-      </c>
-      <c r="N147" t="s" s="2">
-        <v>674</v>
       </c>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
@@ -17878,7 +17874,7 @@
         <v>76</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>74</v>
@@ -17895,10 +17891,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -17995,10 +17991,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -18097,10 +18093,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -18126,13 +18122,13 @@
         <v>98</v>
       </c>
       <c r="L150" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="M150" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="M150" t="s" s="2">
+      <c r="N150" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="N150" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -18182,16 +18178,16 @@
         <v>76</v>
       </c>
       <c r="AF150" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="AG150" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH150" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI150" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="AG150" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH150" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI150" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="AJ150" t="s" s="2">
         <v>91</v>
@@ -18199,10 +18195,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -18228,13 +18224,13 @@
         <v>125</v>
       </c>
       <c r="L151" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="M151" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="M151" t="s" s="2">
+      <c r="N151" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="N151" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -18263,28 +18259,28 @@
         <v>141</v>
       </c>
       <c r="Y151" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="Z151" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="Z151" t="s" s="2">
+      <c r="AA151" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB151" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC151" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD151" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE151" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF151" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="AA151" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB151" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC151" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD151" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE151" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF151" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>74</v>
@@ -18301,10 +18297,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -18330,13 +18326,13 @@
         <v>258</v>
       </c>
       <c r="L152" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="M152" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="M152" t="s" s="2">
+      <c r="N152" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="N152" t="s" s="2">
-        <v>468</v>
       </c>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
@@ -18386,7 +18382,7 @@
         <v>76</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>74</v>
@@ -18403,10 +18399,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -18432,13 +18428,13 @@
         <v>98</v>
       </c>
       <c r="L153" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="M153" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="M153" t="s" s="2">
+      <c r="N153" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="N153" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
@@ -18488,7 +18484,7 @@
         <v>76</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>74</v>
@@ -18505,10 +18501,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -18531,16 +18527,16 @@
         <v>76</v>
       </c>
       <c r="K154" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="L154" t="s" s="2">
         <v>682</v>
       </c>
-      <c r="L154" t="s" s="2">
+      <c r="M154" t="s" s="2">
         <v>683</v>
       </c>
-      <c r="M154" t="s" s="2">
+      <c r="N154" t="s" s="2">
         <v>684</v>
-      </c>
-      <c r="N154" t="s" s="2">
-        <v>685</v>
       </c>
       <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
@@ -18590,7 +18586,7 @@
         <v>76</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>74</v>
@@ -18607,10 +18603,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -18707,10 +18703,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -18809,10 +18805,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -18838,13 +18834,13 @@
         <v>98</v>
       </c>
       <c r="L157" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="M157" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="M157" t="s" s="2">
+      <c r="N157" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="N157" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
@@ -18894,16 +18890,16 @@
         <v>76</v>
       </c>
       <c r="AF157" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="AG157" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH157" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI157" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="AG157" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH157" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI157" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="AJ157" t="s" s="2">
         <v>91</v>
@@ -18911,10 +18907,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -18940,13 +18936,13 @@
         <v>125</v>
       </c>
       <c r="L158" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="M158" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="M158" t="s" s="2">
+      <c r="N158" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="N158" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
@@ -18975,28 +18971,28 @@
         <v>141</v>
       </c>
       <c r="Y158" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="Z158" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="Z158" t="s" s="2">
+      <c r="AA158" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB158" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC158" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD158" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE158" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF158" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="AA158" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB158" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC158" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD158" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE158" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF158" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>74</v>
@@ -19013,10 +19009,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -19042,13 +19038,13 @@
         <v>258</v>
       </c>
       <c r="L159" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="M159" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="M159" t="s" s="2">
+      <c r="N159" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="N159" t="s" s="2">
-        <v>468</v>
       </c>
       <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
@@ -19098,7 +19094,7 @@
         <v>76</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>74</v>
@@ -19115,10 +19111,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -19144,13 +19140,13 @@
         <v>98</v>
       </c>
       <c r="L160" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="M160" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="M160" t="s" s="2">
+      <c r="N160" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="N160" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
@@ -19200,7 +19196,7 @@
         <v>76</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>74</v>
@@ -19217,10 +19213,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -19243,19 +19239,19 @@
         <v>76</v>
       </c>
       <c r="K161" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="L161" t="s" s="2">
         <v>693</v>
       </c>
-      <c r="L161" t="s" s="2">
+      <c r="M161" t="s" s="2">
         <v>694</v>
       </c>
-      <c r="M161" t="s" s="2">
+      <c r="N161" t="s" s="2">
         <v>695</v>
       </c>
-      <c r="N161" t="s" s="2">
+      <c r="O161" t="s" s="2">
         <v>696</v>
-      </c>
-      <c r="O161" t="s" s="2">
-        <v>697</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>76</v>
@@ -19304,7 +19300,7 @@
         <v>76</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>74</v>
@@ -19316,15 +19312,15 @@
         <v>90</v>
       </c>
       <c r="AJ161" t="s" s="2">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -19421,10 +19417,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -19523,14 +19519,14 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E164" s="2"/>
       <c r="F164" t="s" s="2">
@@ -19552,10 +19548,10 @@
         <v>104</v>
       </c>
       <c r="L164" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="M164" t="s" s="2">
         <v>703</v>
-      </c>
-      <c r="M164" t="s" s="2">
-        <v>704</v>
       </c>
       <c r="N164" t="s" s="2">
         <v>107</v>
@@ -19610,7 +19606,7 @@
         <v>76</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>74</v>
@@ -19627,10 +19623,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -19653,16 +19649,16 @@
         <v>76</v>
       </c>
       <c r="K165" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="L165" t="s" s="2">
         <v>707</v>
       </c>
-      <c r="L165" t="s" s="2">
+      <c r="M165" t="s" s="2">
         <v>708</v>
       </c>
-      <c r="M165" t="s" s="2">
+      <c r="N165" t="s" s="2">
         <v>709</v>
-      </c>
-      <c r="N165" t="s" s="2">
-        <v>710</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
@@ -19712,7 +19708,7 @@
         <v>76</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>74</v>
@@ -19721,18 +19717,18 @@
         <v>83</v>
       </c>
       <c r="AI165" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="AJ165" t="s" s="2">
         <v>711</v>
-      </c>
-      <c r="AJ165" t="s" s="2">
-        <v>712</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -19755,16 +19751,16 @@
         <v>76</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="L166" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="M166" t="s" s="2">
         <v>714</v>
       </c>
-      <c r="M166" t="s" s="2">
-        <v>715</v>
-      </c>
       <c r="N166" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
@@ -19814,7 +19810,7 @@
         <v>76</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>74</v>
@@ -19823,18 +19819,18 @@
         <v>83</v>
       </c>
       <c r="AI166" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="AJ166" t="s" s="2">
         <v>711</v>
-      </c>
-      <c r="AJ166" t="s" s="2">
-        <v>712</v>
       </c>
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -19860,16 +19856,16 @@
         <v>282</v>
       </c>
       <c r="L167" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="M167" t="s" s="2">
         <v>717</v>
       </c>
-      <c r="M167" t="s" s="2">
+      <c r="N167" t="s" s="2">
         <v>718</v>
       </c>
-      <c r="N167" t="s" s="2">
+      <c r="O167" t="s" s="2">
         <v>719</v>
-      </c>
-      <c r="O167" t="s" s="2">
-        <v>720</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>76</v>
@@ -19897,11 +19893,11 @@
         <v>163</v>
       </c>
       <c r="Y167" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="Z167" t="s" s="2">
         <v>721</v>
       </c>
-      <c r="Z167" t="s" s="2">
-        <v>722</v>
-      </c>
       <c r="AA167" t="s" s="2">
         <v>76</v>
       </c>
@@ -19918,7 +19914,7 @@
         <v>76</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>74</v>
@@ -19935,10 +19931,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -19964,16 +19960,16 @@
         <v>282</v>
       </c>
       <c r="L168" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="M168" t="s" s="2">
         <v>724</v>
       </c>
-      <c r="M168" t="s" s="2">
+      <c r="N168" t="s" s="2">
         <v>725</v>
       </c>
-      <c r="N168" t="s" s="2">
+      <c r="O168" t="s" s="2">
         <v>726</v>
-      </c>
-      <c r="O168" t="s" s="2">
-        <v>727</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>76</v>
@@ -20001,11 +19997,11 @@
         <v>149</v>
       </c>
       <c r="Y168" t="s" s="2">
+        <v>727</v>
+      </c>
+      <c r="Z168" t="s" s="2">
         <v>728</v>
       </c>
-      <c r="Z168" t="s" s="2">
-        <v>729</v>
-      </c>
       <c r="AA168" t="s" s="2">
         <v>76</v>
       </c>
@@ -20022,7 +20018,7 @@
         <v>76</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>74</v>
@@ -20039,10 +20035,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -20065,19 +20061,19 @@
         <v>76</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="L169" t="s" s="2">
+        <v>730</v>
+      </c>
+      <c r="M169" t="s" s="2">
         <v>731</v>
       </c>
-      <c r="M169" t="s" s="2">
+      <c r="N169" t="s" s="2">
         <v>732</v>
       </c>
-      <c r="N169" t="s" s="2">
+      <c r="O169" t="s" s="2">
         <v>733</v>
-      </c>
-      <c r="O169" t="s" s="2">
-        <v>734</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>76</v>
@@ -20126,7 +20122,7 @@
         <v>76</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>74</v>
@@ -20138,15 +20134,15 @@
         <v>90</v>
       </c>
       <c r="AJ169" t="s" s="2">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -20172,10 +20168,10 @@
         <v>98</v>
       </c>
       <c r="L170" t="s" s="2">
+        <v>736</v>
+      </c>
+      <c r="M170" t="s" s="2">
         <v>737</v>
-      </c>
-      <c r="M170" t="s" s="2">
-        <v>738</v>
       </c>
       <c r="N170" t="s" s="2">
         <v>327</v>
@@ -20228,7 +20224,7 @@
         <v>76</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>74</v>
@@ -20245,10 +20241,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -20271,16 +20267,16 @@
         <v>84</v>
       </c>
       <c r="K171" t="s" s="2">
+        <v>739</v>
+      </c>
+      <c r="L171" t="s" s="2">
         <v>740</v>
       </c>
-      <c r="L171" t="s" s="2">
+      <c r="M171" t="s" s="2">
         <v>741</v>
       </c>
-      <c r="M171" t="s" s="2">
+      <c r="N171" t="s" s="2">
         <v>742</v>
-      </c>
-      <c r="N171" t="s" s="2">
-        <v>743</v>
       </c>
       <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
@@ -20330,7 +20326,7 @@
         <v>76</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>74</v>
@@ -20347,10 +20343,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -20373,16 +20369,16 @@
         <v>84</v>
       </c>
       <c r="K172" t="s" s="2">
+        <v>744</v>
+      </c>
+      <c r="L172" t="s" s="2">
         <v>745</v>
       </c>
-      <c r="L172" t="s" s="2">
+      <c r="M172" t="s" s="2">
         <v>746</v>
       </c>
-      <c r="M172" t="s" s="2">
+      <c r="N172" t="s" s="2">
         <v>747</v>
-      </c>
-      <c r="N172" t="s" s="2">
-        <v>748</v>
       </c>
       <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
@@ -20432,7 +20428,7 @@
         <v>76</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>74</v>
@@ -20449,10 +20445,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -20475,19 +20471,19 @@
         <v>84</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="L173" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="M173" t="s" s="2">
         <v>750</v>
       </c>
-      <c r="M173" t="s" s="2">
+      <c r="N173" t="s" s="2">
         <v>751</v>
       </c>
-      <c r="N173" t="s" s="2">
+      <c r="O173" t="s" s="2">
         <v>752</v>
-      </c>
-      <c r="O173" t="s" s="2">
-        <v>753</v>
       </c>
       <c r="P173" t="s" s="2">
         <v>76</v>
@@ -20536,7 +20532,7 @@
         <v>76</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>74</v>
@@ -20553,10 +20549,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -20653,10 +20649,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -20755,14 +20751,14 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E176" s="2"/>
       <c r="F176" t="s" s="2">
@@ -20784,10 +20780,10 @@
         <v>104</v>
       </c>
       <c r="L176" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="M176" t="s" s="2">
         <v>703</v>
-      </c>
-      <c r="M176" t="s" s="2">
-        <v>704</v>
       </c>
       <c r="N176" t="s" s="2">
         <v>107</v>
@@ -20842,7 +20838,7 @@
         <v>76</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>74</v>
@@ -20859,10 +20855,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -20888,16 +20884,16 @@
         <v>282</v>
       </c>
       <c r="L177" t="s" s="2">
+        <v>757</v>
+      </c>
+      <c r="M177" t="s" s="2">
         <v>758</v>
       </c>
-      <c r="M177" t="s" s="2">
+      <c r="N177" t="s" s="2">
         <v>759</v>
       </c>
-      <c r="N177" t="s" s="2">
-        <v>760</v>
-      </c>
       <c r="O177" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>76</v>
@@ -20925,10 +20921,10 @@
         <v>149</v>
       </c>
       <c r="Y177" t="s" s="2">
-        <v>426</v>
+        <v>760</v>
       </c>
       <c r="Z177" t="s" s="2">
-        <v>427</v>
+        <v>761</v>
       </c>
       <c r="AA177" t="s" s="2">
         <v>76</v>
@@ -20946,7 +20942,7 @@
         <v>76</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>83</v>
@@ -20963,10 +20959,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -20989,19 +20985,19 @@
         <v>84</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="O178" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="P178" t="s" s="2">
         <v>76</v>
@@ -21050,7 +21046,7 @@
         <v>76</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>74</v>
@@ -21067,10 +21063,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -21096,16 +21092,16 @@
         <v>282</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="N179" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="O179" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>76</v>
@@ -21133,10 +21129,10 @@
         <v>141</v>
       </c>
       <c r="Y179" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="Z179" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="AA179" t="s" s="2">
         <v>76</v>
@@ -21154,7 +21150,7 @@
         <v>76</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>74</v>
@@ -21163,7 +21159,7 @@
         <v>83</v>
       </c>
       <c r="AI179" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="AJ179" t="s" s="2">
         <v>91</v>
@@ -21171,14 +21167,14 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="E180" s="2"/>
       <c r="F180" t="s" s="2">
@@ -21200,16 +21196,16 @@
         <v>282</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="N180" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="O180" t="s" s="2">
         <v>637</v>
-      </c>
-      <c r="O180" t="s" s="2">
-        <v>638</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>76</v>
@@ -21237,10 +21233,10 @@
         <v>141</v>
       </c>
       <c r="Y180" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="Z180" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="AA180" t="s" s="2">
         <v>76</v>
@@ -21258,7 +21254,7 @@
         <v>76</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>74</v>
@@ -21275,10 +21271,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -21304,16 +21300,16 @@
         <v>77</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="N181" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="O181" t="s" s="2">
         <v>696</v>
-      </c>
-      <c r="O181" t="s" s="2">
-        <v>697</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>76</v>
@@ -21362,7 +21358,7 @@
         <v>76</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>74</v>

--- a/StructureDefinition-mii-pr-mikrobio-allgemeine-bestimmung.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-allgemeine-bestimmung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:00:57+00:00</t>
+    <t>2026-09-10T16:03:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-mikrobio-allgemeine-bestimmung.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-allgemeine-bestimmung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T16:03:25+00:00</t>
+    <t>2026-09-10T16:53:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-mikrobio-allgemeine-bestimmung.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-allgemeine-bestimmung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T16:53:22+00:00</t>
+    <t>2026-09-10T17:52:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-mikrobio-allgemeine-bestimmung.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-allgemeine-bestimmung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T17:52:15+00:00</t>
+    <t>2026-09-11T12:05:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-mikrobio-allgemeine-bestimmung.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-allgemeine-bestimmung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T12:05:40+00:00</t>
+    <t>2026-09-12T16:32:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-mikrobio-allgemeine-bestimmung.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-allgemeine-bestimmung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T16:32:25+00:00</t>
+    <t>2026-09-12T17:28:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-mikrobio-allgemeine-bestimmung.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-allgemeine-bestimmung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T17:28:38+00:00</t>
+    <t>2026-09-12T20:31:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
